--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-18.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-18.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_traning_lay0x0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_52FDFC8857D9EC27CB3A2211595ED87656CD6F10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D95A6DD4-1173-4362-A9F1-6D5351083FCE}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_52FDFC8857D9EC27CB3A2211595ED87656CD6F10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80DEA727-09B5-4C1B-83C9-6AD53C860671}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sinais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -775,6 +788,10 @@
       <c r="I2">
         <v>11.76</v>
       </c>
+      <c r="J2" t="str">
+        <f>IF(M2=1,"GREEN", "RED")</f>
+        <v>GREEN</v>
+      </c>
       <c r="L2" t="s">
         <v>18</v>
       </c>
@@ -810,6 +827,10 @@
       <c r="I3">
         <v>15.38</v>
       </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J29" si="0">IF(M3=1,"GREEN", "RED")</f>
+        <v>GREEN</v>
+      </c>
       <c r="L3" t="s">
         <v>18</v>
       </c>
@@ -845,6 +866,10 @@
       <c r="I4">
         <v>11.43</v>
       </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L4" t="s">
         <v>18</v>
       </c>
@@ -880,6 +905,10 @@
       <c r="I5">
         <v>14.29</v>
       </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L5" t="s">
         <v>18</v>
       </c>
@@ -915,6 +944,10 @@
       <c r="I6">
         <v>6.45</v>
       </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L6" t="s">
         <v>18</v>
       </c>
@@ -950,6 +983,10 @@
       <c r="I7">
         <v>11.11</v>
       </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L7" t="s">
         <v>18</v>
       </c>
@@ -985,6 +1022,10 @@
       <c r="I8">
         <v>13.79</v>
       </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L8" t="s">
         <v>18</v>
       </c>
@@ -1020,6 +1061,10 @@
       <c r="I9">
         <v>12.5</v>
       </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L9" t="s">
         <v>18</v>
       </c>
@@ -1055,6 +1100,10 @@
       <c r="I10">
         <v>13.33</v>
       </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
@@ -1090,6 +1139,10 @@
       <c r="I11">
         <v>9.09</v>
       </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L11" t="s">
         <v>18</v>
       </c>
@@ -1125,6 +1178,10 @@
       <c r="I12">
         <v>11.76</v>
       </c>
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L12" t="s">
         <v>18</v>
       </c>
@@ -1160,6 +1217,10 @@
       <c r="I13">
         <v>9.52</v>
       </c>
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L13" t="s">
         <v>18</v>
       </c>
@@ -1195,11 +1256,15 @@
       <c r="I14">
         <v>8.33</v>
       </c>
+      <c r="J14" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
       <c r="L14" t="s">
         <v>18</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1230,6 +1295,10 @@
       <c r="I15">
         <v>9.52</v>
       </c>
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L15" t="s">
         <v>18</v>
       </c>
@@ -1265,6 +1334,10 @@
       <c r="I16">
         <v>11.43</v>
       </c>
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L16" t="s">
         <v>18</v>
       </c>
@@ -1272,7 +1345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1300,11 +1373,18 @@
       <c r="I17">
         <v>18.18</v>
       </c>
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1332,11 +1412,18 @@
       <c r="I18">
         <v>21.05</v>
       </c>
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1364,11 +1451,18 @@
       <c r="I19">
         <v>21.05</v>
       </c>
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1396,11 +1490,18 @@
       <c r="I20">
         <v>10</v>
       </c>
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1428,11 +1529,18 @@
       <c r="I21">
         <v>20</v>
       </c>
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1460,11 +1568,18 @@
       <c r="I22">
         <v>20</v>
       </c>
+      <c r="J22" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L22" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1492,11 +1607,18 @@
       <c r="I23">
         <v>18.18</v>
       </c>
+      <c r="J23" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L23" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1524,11 +1646,18 @@
       <c r="I24">
         <v>14.29</v>
       </c>
+      <c r="J24" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L24" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1556,11 +1685,18 @@
       <c r="I25">
         <v>3.7</v>
       </c>
+      <c r="J25" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L25" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1588,11 +1724,18 @@
       <c r="I26">
         <v>19.05</v>
       </c>
+      <c r="J26" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L26" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1620,11 +1763,18 @@
       <c r="I27">
         <v>13.79</v>
       </c>
+      <c r="J27" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L27" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1652,11 +1802,18 @@
       <c r="I28">
         <v>12.5</v>
       </c>
+      <c r="J28" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1684,8 +1841,15 @@
       <c r="I29">
         <v>11.11</v>
       </c>
+      <c r="J29" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L29" t="s">
         <v>18</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
